--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260915.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260915.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>611,770,000</t>
+          <t>613,200,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.24%</t>
+          <t>15.03%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>685,780,000</t>
+          <t>686,810,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.48%</t>
+          <t>12.26%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>10.08%</t>
+          <t>10.35%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>179,740,000</t>
+          <t>179,850,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>9.67%</t>
+          <t>9.72%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.85%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.44%</t>
+          <t>5.36%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>99,203,000</t>
+          <t>100,043,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
@@ -792,271 +792,271 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>1,832</t>
+          <t>23,380,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>23,380,000</t>
+          <t>139,840,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>139,840,000</t>
+          <t>251,824,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>249,124,000</t>
+          <t>75,890,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>75,890,000</t>
+          <t>11,520,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>11,520,000</t>
+          <t>209,810,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>209,810,000</t>
+          <t>64,910,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>64,910,000</t>
+          <t>103,700,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>102,200,000</t>
+          <t>25,720,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>遠雄</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>25,720,000</t>
+          <t>70,789,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>遠雄</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>70,789,000</t>
+          <t>36,460,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>36,460,000</t>
+          <t>119,660,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1078,161 +1078,161 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>119,660,000</t>
+          <t>77,000,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>77,000,000</t>
+          <t>35,270,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>34,760,000</t>
+          <t>8,564,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>8,564,000</t>
+          <t>12,488,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>12,488,000</t>
+          <t>39,933,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>39,353,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>36,840,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1261,22 +1261,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>36,840,000</t>
+          <t>14,300,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1298,29 +1298,29 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>14,300,000</t>
+          <t>27,940,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1371,22 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>27,940,000</t>
+          <t>13,530,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1408,29 +1408,29 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>13,530,000</t>
+          <t>29,096,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1452,68 +1452,64 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>29,096,000</t>
+          <t>20,590,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>B20258</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>P14台泥1A</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>20,590,000</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>0.27%</t>
-        </is>
-      </c>
+          <t>760,000,000</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>B20258</t>
+          <t>B402BR</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>P14台泥1A</t>
+          <t>P14台塑1</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>190,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
@@ -1521,12 +1517,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>B92365</t>
+          <t>B618CS</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>P14遠鼎2B</t>
+          <t>P10台積6A</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1539,17 +1535,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>B96524</t>
+          <t>B644B6</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>P11元金1</t>
+          <t>P07鴻海1E</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>150,000,000</t>
+          <t>66,000,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
@@ -1557,17 +1553,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>B99503</t>
+          <t>B801AE</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>P12富壽1A</t>
+          <t>02中鋼1C</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>110,000,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr"/>
@@ -1575,17 +1571,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>B99607</t>
+          <t>B903ZC</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>P13國壽1A</t>
+          <t>P12台電6A</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
@@ -1593,17 +1589,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>B92365</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>P14遠鼎2B</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>13,725,627,663</t>
+          <t>160,000,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
@@ -1611,17 +1607,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>B92603</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>P13永昌證1</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,168,488,986</t>
+          <t>119,000,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr"/>
@@ -1629,20 +1625,308 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>B95146</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>P14中租1A</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>100,000,000</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>B95459</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>P09中控2C</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>100,000,000</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>B96524</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>P11元金1</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>150,000,000</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>B98412</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>P11奇美1</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>105,000,000</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>B98907</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>P09國泰金2</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>400,000,000</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>B98914</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>P12國泰金1B</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>B99503</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>P12富壽1A</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>100,000,000</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>B99607</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>P13國壽1A</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>200,000,000</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>B9A609</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>P13元大證1</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>10,000,000</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>14,678,931,081</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>G10323</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>P14高銀2</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>30,000,000</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>G107CP</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>P15北富銀1A</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>G11748</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>P15王道銀1A</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>60,000,000</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>G139AL</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>P13遠銀1A</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>10,000,000</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>G139AN</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>P14遠銀1</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>240,000,000</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>M_NTD</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>MARGIN</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>2,147,934,603</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
           <t>RDI_NTD</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>-585,302,415</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr"/>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>-844,482,411</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
